--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484367_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484367_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1227</v>
+        <v>4.946</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2118</v>
+        <v>3.8989</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9109</v>
+        <v>1.047</v>
       </c>
       <c r="G2" t="n">
         <v>4.7335</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1789</v>
+        <v>1.0022</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1594</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3383</v>
+        <v>0.4745</v>
       </c>
       <c r="V2" t="n">
         <v>1.1638</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6333</v>
+        <v>1.6716</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6474</v>
+        <v>2.4133</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0141</v>
+        <v>-0.7418</v>
       </c>
       <c r="G3" t="n">
         <v>-2.2237</v>
@@ -688,13 +688,13 @@
         <v>2.1488</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9841</v>
+        <v>3.0224</v>
       </c>
       <c r="T3" t="n">
-        <v>3.6293</v>
+        <v>2.3952</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3548</v>
+        <v>0.6271</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2992</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9546</v>
+        <v>1.1101</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9974</v>
+        <v>1.0985</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0428</v>
+        <v>0.0116</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0445</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2196</v>
+        <v>-0.064</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1816</v>
+        <v>-0.0805</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.038</v>
+        <v>0.0165</v>
       </c>
       <c r="V4" t="n">
         <v>1.2186</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7355</v>
+        <v>0.545</v>
       </c>
       <c r="E5" t="n">
-        <v>1.244</v>
+        <v>0.4342</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5085</v>
+        <v>0.1108</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5301</v>
+        <v>-1.0995</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3446</v>
+        <v>1.0317</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8746</v>
+        <v>-2.1313</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1615</v>
+        <v>0.8832</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4988</v>
+        <v>1.3955</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6603</v>
+        <v>-0.5122</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3686</v>
+        <v>-1.9828</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1542</v>
+        <v>-0.3638</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2144</v>
+        <v>-1.619</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2876</v>
+        <v>1.2443</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1049</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1826</v>
+        <v>0.7166</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0219</v>
+        <v>-0.5764</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2992</v>
+        <v>-0.5764</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MONTANER BRIERA</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0588</v>
+        <v>0.3334</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7478</v>
+        <v>0.5967</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6889</v>
+        <v>-0.2633</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.196</v>
+        <v>-1.5301</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7079</v>
+        <v>0.3446</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9039</v>
+        <v>-1.8746</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0228</v>
+        <v>-0.1615</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.4988</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>-0.6603</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2188</v>
+        <v>-1.3686</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2745</v>
+        <v>-0.1542</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9443</v>
+        <v>-1.2144</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6455</v>
+        <v>1.8854</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7016</v>
+        <v>1.4577</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0561</v>
+        <v>0.4277</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.0219</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2992</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>M. BALLÚS TORRAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0604</v>
+        <v>-0.1128</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2529</v>
+        <v>-0.2859</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1925</v>
+        <v>0.1731</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0995</v>
+        <v>-1.0537</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0317</v>
+        <v>1.5626</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1313</v>
+        <v>-2.6163</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8832</v>
+        <v>0.7793</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3955</v>
+        <v>2.0466</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5122</v>
+        <v>-1.2673</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9828</v>
+        <v>-1.833</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3638</v>
+        <v>-0.484</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.619</v>
+        <v>-1.349</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6388</v>
+        <v>0.5173</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1594</v>
+        <v>0.2436</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7983</v>
+        <v>0.2737</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5764</v>
+        <v>0.0329</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5764</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>M. MONTANER BRIERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6461</v>
+        <v>-0.3184</v>
       </c>
       <c r="E8" t="n">
-        <v>0.426</v>
+        <v>0.3433</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.072</v>
+        <v>-0.6617</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.9917</v>
+        <v>-0.196</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.548</v>
+        <v>0.7079</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4437</v>
+        <v>-0.9039</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8741</v>
+        <v>1.0228</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9146</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1176</v>
+        <v>-1.2188</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6334</v>
+        <v>-0.2745</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4842</v>
+        <v>-0.9443</v>
       </c>
       <c r="P8" t="n">
-        <v>0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3689</v>
+        <v>0.2683</v>
       </c>
       <c r="T8" t="n">
-        <v>1.6675</v>
+        <v>0.2972</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7014</v>
+        <v>-0.0289</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. BALLÚS TORRAS</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8678</v>
+        <v>-0.4827</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0137</v>
+        <v>0.4593</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1459</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0537</v>
+        <v>-1.7463</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5626</v>
+        <v>0.0072</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6163</v>
+        <v>-1.7534</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7793</v>
+        <v>-0.243</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0466</v>
+        <v>0.431</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2673</v>
+        <v>-0.6741</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.833</v>
+        <v>-1.5032</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.484</v>
+        <v>-0.4239</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.349</v>
+        <v>-1.0793</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2377</v>
+        <v>0.6775</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4842</v>
+        <v>0.7024</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2465</v>
+        <v>-0.0248</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0329</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3321</v>
+        <v>-0.6788</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1182</v>
+        <v>0.826</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4503</v>
+        <v>-1.5048</v>
       </c>
       <c r="G10" t="n">
         <v>-3.2586</v>
@@ -1234,13 +1234,13 @@
         <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2938</v>
+        <v>0.9472</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1432</v>
+        <v>0.851</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1507</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>1.8279</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6494</v>
+        <v>-1.1668</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6529</v>
+        <v>0.0414</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9965000000000001</v>
+        <v>-1.2082</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7463</v>
+        <v>-2.9917</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0072</v>
+        <v>-1.548</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7534</v>
+        <v>-1.4437</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.243</v>
+        <v>-0.8741</v>
       </c>
       <c r="K11" t="n">
-        <v>0.431</v>
+        <v>-0.9146</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6741</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5032</v>
+        <v>-2.1176</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4239</v>
+        <v>-0.6334</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0793</v>
+        <v>-1.4842</v>
       </c>
       <c r="P11" t="n">
         <v>0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4892</v>
+        <v>1.8482</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4099</v>
+        <v>1.283</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0793</v>
+        <v>0.5653</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0142</v>
+        <v>-2.9379</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7089</v>
+        <v>-1.9518</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3053</v>
+        <v>-0.9862</v>
       </c>
       <c r="G12" t="n">
         <v>-4.8466</v>
@@ -1390,13 +1390,13 @@
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0496</v>
+        <v>1.1259</v>
       </c>
       <c r="T12" t="n">
-        <v>0.71</v>
+        <v>0.4672</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3396</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0.5874</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0585</v>
+        <v>-5.0234</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1488</v>
+        <v>-3.2499</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9096</v>
+        <v>-1.7735</v>
       </c>
       <c r="G13" t="n">
         <v>-4.5283</v>
@@ -1468,13 +1468,13 @@
         <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1926</v>
+        <v>0.2277</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4458</v>
+        <v>0.3447</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2532</v>
+        <v>-0.117</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3321</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.123599999999999</v>
+        <v>-2.114699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>3.615399999999999</v>
+        <v>4.623999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.7387</v>
+        <v>-6.739</v>
       </c>
       <c r="G14" t="n">
         <v>-18.7855</v>
@@ -1519,7 +1519,7 @@
         <v>-22.2531</v>
       </c>
       <c r="J14" t="n">
-        <v>3.040199999999999</v>
+        <v>3.0402</v>
       </c>
       <c r="K14" t="n">
         <v>8.429</v>
@@ -1546,13 +1546,13 @@
         <v>13.6739</v>
       </c>
       <c r="S14" t="n">
-        <v>11.6933</v>
+        <v>12.7024</v>
       </c>
       <c r="T14" t="n">
-        <v>8.0078</v>
+        <v>9.0169</v>
       </c>
       <c r="U14" t="n">
-        <v>3.6856</v>
+        <v>3.6857</v>
       </c>
       <c r="V14" t="n">
         <v>2.9917</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4107</v>
+        <v>5.0613</v>
       </c>
       <c r="E15" t="n">
-        <v>3.311</v>
+        <v>4.0188</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0997</v>
+        <v>1.0425</v>
       </c>
       <c r="G15" t="n">
         <v>7.8666</v>
@@ -1624,13 +1624,13 @@
         <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.4439</v>
+        <v>-1.7933</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.392</v>
+        <v>-0.6842</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0519</v>
+        <v>-1.109</v>
       </c>
       <c r="V15" t="n">
         <v>0.9414</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0516</v>
+        <v>4.4571</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7512</v>
+        <v>3.459</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3004</v>
+        <v>0.9981</v>
       </c>
       <c r="G16" t="n">
         <v>3.7193</v>
@@ -1702,13 +1702,13 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.2304</v>
+        <v>-1.8249</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4993</v>
+        <v>-0.7915</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7311</v>
+        <v>-1.0334</v>
       </c>
       <c r="V16" t="n">
         <v>0.6093</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1409</v>
+        <v>2.7818</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2751</v>
+        <v>1.9717</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8659</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>1.7309</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4919</v>
+        <v>0.1327</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3853</v>
+        <v>0.0819</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1066</v>
+        <v>0.0508</v>
       </c>
       <c r="V17" t="n">
         <v>0.3321</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0443</v>
+        <v>0.7623</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8182</v>
+        <v>2.9193</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.8625</v>
+        <v>-2.1571</v>
       </c>
       <c r="G18" t="n">
         <v>4.7983</v>
@@ -1858,13 +1858,13 @@
         <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.1514</v>
+        <v>-2.3448</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8995</v>
+        <v>-0.7984</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.2519</v>
+        <v>-1.5465</v>
       </c>
       <c r="V18" t="n">
         <v>-1.4959</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6028</v>
+        <v>-0.4122</v>
       </c>
       <c r="E19" t="n">
         <v>0.0921</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6949</v>
+        <v>-0.5042</v>
       </c>
       <c r="G19" t="n">
         <v>1.5283</v>
@@ -1936,13 +1936,13 @@
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4632</v>
+        <v>-1.2725</v>
       </c>
       <c r="T19" t="n">
         <v>-0.2283</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2349</v>
+        <v>-1.0442</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2772</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1572</v>
+        <v>-1.0262</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7321</v>
+        <v>0.4288</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8894</v>
+        <v>-1.4549</v>
       </c>
       <c r="G20" t="n">
         <v>0.8151</v>
@@ -2014,13 +2014,13 @@
         <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.949</v>
+        <v>-1.818</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1127</v>
+        <v>-0.416</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.8363</v>
+        <v>-1.4019</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6093</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1672</v>
+        <v>-1.0311</v>
       </c>
       <c r="E21" t="n">
         <v>-1.2066</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0394</v>
+        <v>0.1755</v>
       </c>
       <c r="G21" t="n">
         <v>0.7697000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3742</v>
+        <v>-0.238</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1816</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1926</v>
+        <v>-0.0565</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6284</v>
+        <v>-3.0264</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9634</v>
+        <v>-1.469</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.665</v>
+        <v>-1.5574</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5969</v>
@@ -2170,13 +2170,13 @@
         <v>1.9534</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0699</v>
+        <v>-0.3281</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3331</v>
+        <v>-0.1725</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2632</v>
+        <v>-0.1556</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8828</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8796</v>
+        <v>-3.0948</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0708</v>
+        <v>-3.4753</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1912</v>
+        <v>0.3805</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8457</v>
@@ -2248,13 +2248,13 @@
         <v>2.1488</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6432</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0906</v>
+        <v>-0.495</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5526</v>
+        <v>-0.3633</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6093</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.123699999999999</v>
+        <v>4.471799999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>6.738899999999999</v>
+        <v>6.7388</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.615199999999999</v>
+        <v>-2.267</v>
       </c>
       <c r="G24" t="n">
         <v>18.7856</v>
@@ -2326,13 +2326,13 @@
         <v>12.6972</v>
       </c>
       <c r="S24" t="n">
-        <v>-11.6935</v>
+        <v>-10.3453</v>
       </c>
       <c r="T24" t="n">
         <v>-3.6856</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.007899999999999</v>
+        <v>-6.6596</v>
       </c>
       <c r="V24" t="n">
         <v>-2.9917</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484367_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484367_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5764</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.545</v>
+        <v>0.921</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4342</v>
+        <v>0.921</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1108</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0995</v>
+        <v>0.921</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0317</v>
+        <v>0.921</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1313</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8832</v>
+        <v>0.921</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3955</v>
+        <v>0.921</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5122</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9828</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3638</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.619</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2443</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5276999999999999</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7166</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5764</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5764</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3334</v>
+        <v>0.545</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5967</v>
+        <v>0.4342</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2633</v>
+        <v>0.1108</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5301</v>
+        <v>-1.0995</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3446</v>
+        <v>1.0317</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8746</v>
+        <v>-2.1313</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1615</v>
+        <v>0.8832</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4988</v>
+        <v>1.3955</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6603</v>
+        <v>-0.5122</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3686</v>
+        <v>-1.9828</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1542</v>
+        <v>-0.3638</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2144</v>
+        <v>-1.619</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8854</v>
+        <v>1.2443</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4577</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4277</v>
+        <v>0.7166</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0219</v>
+        <v>-0.5764</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2992</v>
+        <v>-0.5764</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BALLÚS TORRAS</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1128</v>
+        <v>0.3334</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2859</v>
+        <v>0.5967</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1731</v>
+        <v>-0.2633</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0537</v>
+        <v>-1.5301</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5626</v>
+        <v>0.3446</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.6163</v>
+        <v>-1.8746</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7793</v>
+        <v>-0.1615</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0466</v>
+        <v>0.4988</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2673</v>
+        <v>-0.6603</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.833</v>
+        <v>-1.3686</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.484</v>
+        <v>-0.1542</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.349</v>
+        <v>-1.2144</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5173</v>
+        <v>1.8854</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2436</v>
+        <v>1.4577</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2737</v>
+        <v>0.4277</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0329</v>
+        <v>-0.0219</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>0.365</v>
+        <v>-0.2992</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MONTANER BRIERA</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3184</v>
+        <v>0.307</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3433</v>
+        <v>0.307</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6617</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.196</v>
+        <v>0.307</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7079</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9039</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0228</v>
+        <v>0.307</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2188</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2745</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9443</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2683</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2972</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0289</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1094,12 +1129,17 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>M. BALLUS TORRAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4827</v>
+        <v>-0.1128</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4593</v>
+        <v>-0.2859</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9419999999999999</v>
+        <v>0.1731</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7463</v>
+        <v>-1.0537</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0072</v>
+        <v>1.5626</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7534</v>
+        <v>-2.6163</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.243</v>
+        <v>0.7793</v>
       </c>
       <c r="K9" t="n">
-        <v>0.431</v>
+        <v>2.0466</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6741</v>
+        <v>-1.2673</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5032</v>
+        <v>-1.833</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4239</v>
+        <v>-0.484</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0793</v>
+        <v>-1.349</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6775</v>
+        <v>0.5173</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7024</v>
+        <v>0.2436</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0248</v>
+        <v>0.2737</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.0329</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.365</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>M. MONTANER BRIERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6788</v>
+        <v>-0.3184</v>
       </c>
       <c r="E10" t="n">
-        <v>0.826</v>
+        <v>0.3433</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5048</v>
+        <v>-0.6617</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2586</v>
+        <v>-0.196</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5175</v>
+        <v>0.7079</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.7761</v>
+        <v>-0.9039</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8762</v>
+        <v>1.0228</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1461</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0223</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3824</v>
+        <v>-1.2188</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.2745</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7538</v>
+        <v>-0.9443</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9472</v>
+        <v>0.2683</v>
       </c>
       <c r="T10" t="n">
-        <v>0.851</v>
+        <v>0.2972</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09619999999999999</v>
+        <v>-0.0289</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1668</v>
+        <v>-0.4827</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0414</v>
+        <v>0.4593</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2082</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9917</v>
+        <v>-1.7463</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.548</v>
+        <v>0.0072</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4437</v>
+        <v>-1.7534</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8741</v>
+        <v>-0.243</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9146</v>
+        <v>0.431</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0405</v>
+        <v>-0.6741</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1176</v>
+        <v>-1.5032</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6334</v>
+        <v>-0.4239</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4842</v>
+        <v>-1.0793</v>
       </c>
       <c r="P11" t="n">
         <v>0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8482</v>
+        <v>0.6775</v>
       </c>
       <c r="T11" t="n">
-        <v>1.283</v>
+        <v>0.7024</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5653</v>
+        <v>-0.0248</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9379</v>
+        <v>-0.9858</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9518</v>
+        <v>0.519</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9862</v>
+        <v>-1.5048</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.8466</v>
+        <v>-3.5656</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7197</v>
+        <v>0.2106</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.1269</v>
+        <v>-3.7761</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.3288</v>
+        <v>-1.1832</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0349</v>
+        <v>0.8391</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2939</v>
+        <v>-2.0223</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5178</v>
+        <v>-2.3824</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3152</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.833</v>
+        <v>-1.7538</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1953</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1259</v>
+        <v>0.9472</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4672</v>
+        <v>0.851</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5874</v>
+        <v>1.8279</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8865</v>
+        <v>1.8279</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2992</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0234</v>
+        <v>-2.0877</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2499</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7735</v>
+        <v>-1.2082</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.5283</v>
+        <v>-3.9127</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2131</v>
+        <v>-2.469</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.3152</v>
+        <v>-1.4437</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.2858</v>
+        <v>-1.7951</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4106</v>
+        <v>-1.8356</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6964</v>
+        <v>0.0405</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2425</v>
+        <v>-2.1176</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6237</v>
+        <v>-0.6334</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.6188</v>
+        <v>-1.4842</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2277</v>
+        <v>1.8482</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3447</v>
+        <v>1.283</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.117</v>
+        <v>0.5653</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3321</v>
+        <v>-0.6093</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3321</v>
+        <v>0.6093</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,229 +1566,240 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.114699999999999</v>
+        <v>-2.9379</v>
       </c>
       <c r="E14" t="n">
-        <v>4.623999999999999</v>
+        <v>-1.9518</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.739</v>
+        <v>-0.9862</v>
       </c>
       <c r="G14" t="n">
-        <v>-18.7855</v>
+        <v>-4.8466</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4677</v>
+        <v>-0.7197</v>
       </c>
       <c r="I14" t="n">
-        <v>-22.2531</v>
+        <v>-4.1269</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0402</v>
+        <v>-2.3288</v>
       </c>
       <c r="K14" t="n">
-        <v>8.429</v>
+        <v>-1.0349</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.3888</v>
+        <v>-1.2939</v>
       </c>
       <c r="M14" t="n">
-        <v>-21.8258</v>
+        <v>-2.5178</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.9615</v>
+        <v>0.3152</v>
       </c>
       <c r="O14" t="n">
-        <v>-16.8642</v>
+        <v>-2.833</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9766999999999999</v>
+        <v>0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.6972</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>13.6739</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>12.7024</v>
+        <v>1.1259</v>
       </c>
       <c r="T14" t="n">
-        <v>9.0169</v>
+        <v>0.4672</v>
       </c>
       <c r="U14" t="n">
-        <v>3.6857</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>2.9917</v>
+        <v>0.5874</v>
       </c>
       <c r="W14" t="n">
-        <v>5.264200000000001</v>
+        <v>0.8865</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.2727</v>
+        <v>-0.2992</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0613</v>
+        <v>-5.0234</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0188</v>
+        <v>-3.2499</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0425</v>
+        <v>-1.7735</v>
       </c>
       <c r="G15" t="n">
-        <v>7.8666</v>
+        <v>-4.5283</v>
       </c>
       <c r="H15" t="n">
-        <v>1.23</v>
+        <v>-0.2131</v>
       </c>
       <c r="I15" t="n">
-        <v>6.6366</v>
+        <v>-4.3152</v>
       </c>
       <c r="J15" t="n">
-        <v>8.055400000000001</v>
+        <v>-2.2858</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4968</v>
+        <v>0.4106</v>
       </c>
       <c r="L15" t="n">
-        <v>5.5586</v>
+        <v>-2.6964</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1888</v>
+        <v>-2.2425</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2668</v>
+        <v>-0.6237</v>
       </c>
       <c r="O15" t="n">
-        <v>1.078</v>
+        <v>-1.6188</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.9534</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7933</v>
+        <v>0.2277</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6842</v>
+        <v>0.3447</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.109</v>
+        <v>-0.117</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9414</v>
+        <v>-0.3321</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5545</v>
+        <v>-0.3321</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CB ANDRATX</t>
+          <t>C.B. GRANOLLERS</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.4571</v>
+        <v>-2.1146</v>
       </c>
       <c r="E16" t="n">
-        <v>3.459</v>
+        <v>4.624099999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9981</v>
+        <v>-6.739</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7193</v>
+        <v>-18.7855</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7767</v>
+        <v>3.467800000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9426</v>
+        <v>-22.2531</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9733</v>
+        <v>3.0402</v>
       </c>
       <c r="K16" t="n">
-        <v>2.704</v>
+        <v>8.429</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2692</v>
+        <v>-5.3888</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.254</v>
+        <v>-21.8258</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9273</v>
+        <v>-4.961500000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6733</v>
+        <v>-16.8642</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9534</v>
+        <v>0.9766999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-12.6972</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>13.6739</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8249</v>
+        <v>12.7024</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7915</v>
+        <v>9.0169</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0334</v>
+        <v>3.685700000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6093</v>
+        <v>2.9917</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>5.264200000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3321</v>
-      </c>
+        <v>-2.2727</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DIAGNE YADE</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7818</v>
+        <v>5.0613</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9717</v>
+        <v>4.0188</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.0425</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7309</v>
+        <v>7.8666</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6562</v>
+        <v>1.23</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3871</v>
+        <v>6.6366</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0851</v>
+        <v>8.055400000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1023</v>
+        <v>2.4968</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9828</v>
+        <v>5.5586</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3542</v>
+        <v>-0.1888</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7585</v>
+        <v>-1.2668</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4043</v>
+        <v>1.078</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-3.9069</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1327</v>
+        <v>-1.7933</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0819</v>
+        <v>-0.6842</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0508</v>
+        <v>-1.109</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3321</v>
+        <v>0.9414</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3321</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7623</v>
+        <v>4.4571</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9193</v>
+        <v>3.459</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1571</v>
+        <v>0.9981</v>
       </c>
       <c r="G18" t="n">
-        <v>4.7983</v>
+        <v>3.7193</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9803</v>
+        <v>1.7767</v>
       </c>
       <c r="I18" t="n">
-        <v>2.818</v>
+        <v>1.9426</v>
       </c>
       <c r="J18" t="n">
-        <v>4.6479</v>
+        <v>3.9733</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5032</v>
+        <v>2.704</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1447</v>
+        <v>1.2692</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1505</v>
+        <v>-0.254</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5228</v>
+        <v>-0.9273</v>
       </c>
       <c r="O18" t="n">
         <v>0.6733</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>1.9534</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.3448</v>
+        <v>-1.8249</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7984</v>
+        <v>-0.7915</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.5465</v>
+        <v>-1.0334</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4959</v>
+        <v>0.6093</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.7145</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. PERONA MARCH</t>
+          <t>A. DIAGNE YADE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4122</v>
+        <v>2.7818</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0921</v>
+        <v>1.9717</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5042</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5283</v>
+        <v>1.7309</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6298</v>
+        <v>-0.6562</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1581</v>
+        <v>2.3871</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4924</v>
+        <v>2.0851</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1433</v>
+        <v>0.1023</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3492</v>
+        <v>1.9828</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0359</v>
+        <v>-0.3542</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7731</v>
+        <v>-0.7585</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8089</v>
+        <v>0.4043</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R19" t="n">
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2725</v>
+        <v>0.1327</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2283</v>
+        <v>0.0819</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0442</v>
+        <v>0.0508</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0262</v>
+        <v>0.7623</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4288</v>
+        <v>2.9193</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4549</v>
+        <v>-2.1571</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8151</v>
+        <v>4.7983</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5874</v>
+        <v>1.9803</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4025</v>
+        <v>2.818</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8448</v>
+        <v>4.6479</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0975</v>
+        <v>2.5032</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9424</v>
+        <v>2.1447</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0297</v>
+        <v>0.1505</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5102</v>
+        <v>-0.5228</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5399</v>
+        <v>0.6733</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.818</v>
+        <v>-2.3448</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.416</v>
+        <v>-0.7984</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.4019</v>
+        <v>-1.5465</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6093</v>
+        <v>-1.4959</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>M. PERONA MARCH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0311</v>
+        <v>-0.4122</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2066</v>
+        <v>0.0921</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1755</v>
+        <v>-0.5042</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7697000000000001</v>
+        <v>1.5283</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2034</v>
+        <v>-0.6298</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5663</v>
+        <v>2.1581</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1238</v>
+        <v>1.4924</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9619</v>
+        <v>0.1433</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1619</v>
+        <v>1.3492</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.354</v>
+        <v>0.0359</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7585</v>
+        <v>-0.7731</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4045</v>
+        <v>0.8089</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5627</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.238</v>
+        <v>-1.2725</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1816</v>
+        <v>-0.2283</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0565</v>
+        <v>-1.0442</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0264</v>
+        <v>-1.0262</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.469</v>
+        <v>0.4288</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5574</v>
+        <v>-1.4549</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5969</v>
+        <v>0.8151</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.107</v>
+        <v>-0.5874</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5101</v>
+        <v>1.4025</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6788999999999999</v>
+        <v>0.8448</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.976</v>
+        <v>-1.0975</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2971</v>
+        <v>1.9424</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.918</v>
+        <v>-0.0297</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.131</v>
+        <v>0.5102</v>
       </c>
       <c r="O22" t="n">
-        <v>1.213</v>
+        <v>-0.5399</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3281</v>
+        <v>-1.818</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1725</v>
+        <v>-0.416</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1556</v>
+        <v>-1.4019</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8828</v>
+        <v>-0.6093</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0948</v>
+        <v>-1.0311</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4753</v>
+        <v>-1.2066</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3805</v>
+        <v>0.1755</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8457</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.6777</v>
+        <v>0.2034</v>
       </c>
       <c r="I23" t="n">
-        <v>2.832</v>
+        <v>0.5663</v>
       </c>
       <c r="J23" t="n">
-        <v>0.282</v>
+        <v>1.1238</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.8765</v>
+        <v>0.9619</v>
       </c>
       <c r="L23" t="n">
-        <v>2.1585</v>
+        <v>0.1619</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1277</v>
+        <v>-0.354</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8012</v>
+        <v>-0.7585</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6735</v>
+        <v>0.4045</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7814</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9301</v>
+        <v>-2.1488</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.238</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.495</v>
+        <v>-0.1816</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3633</v>
+        <v>-0.0565</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-3.0264</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.469</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.5574</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.5969</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-3.107</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.5101</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.6788999999999999</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.976</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.918</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-2.131</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.3281</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.1725</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.1556</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.8828</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P. JOVER SANS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.0948</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.4753</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.8457</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-3.6777</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.8765</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2.1585</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.1277</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.8012</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.6735</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.8584000000000001</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.495</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.3633</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484367_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB ANDRATX</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>4.471799999999999</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>6.7388</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>-2.267</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>18.7856</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H26" t="n">
         <v>-3.467700000000001</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I26" t="n">
         <v>22.2533</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J26" t="n">
         <v>21.8258</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K26" t="n">
         <v>4.9615</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>16.8644</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>-3.04</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>-8.429</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O26" t="n">
         <v>5.3889</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>-0.9767000000000001</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-13.6741</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>12.6972</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>-10.3453</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>-3.6856</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>-6.6596</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>-2.9917</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>2.2727</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-5.264399999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
